--- a/IT23650220_Assignment 1 - Test cases.xlsx
+++ b/IT23650220_Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wikum Surindu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wikum Surindu\Videos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18E131D2-02DA-4AE0-B7DC-728B57D27F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98FE8C57-4485-4A9E-B0A9-4D8EC4068956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="237">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -482,9 +482,6 @@
   </si>
   <si>
     <t>Neg_0049</t>
-  </si>
-  <si>
-    <t>L</t>
   </si>
   <si>
     <t>machan mta adha meeting ekee Zoom link eka email ekak vidihata evanna puluwandha? Please send it before 3pm. Mama office yanna kalin check karanna oonea. Email ekak evanna amaarunam WhatsApp msg ekak dhaapan. Thx!</t>
@@ -793,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -820,6 +817,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1052,10 +1052,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1072,16 +1072,16 @@
         <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.8" customHeight="1">
@@ -1098,16 +1098,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1124,16 +1124,16 @@
         <v>16</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.8" customHeight="1">
@@ -1150,16 +1150,16 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1176,16 +1176,16 @@
         <v>22</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28.8" customHeight="1">
@@ -1202,16 +1202,16 @@
         <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I7" s="5"/>
     </row>
@@ -1219,8 +1219,8 @@
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
+      <c r="B8" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>27</v>
@@ -1229,23 +1229,23 @@
         <v>28</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.8" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1255,16 +1255,16 @@
         <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1281,16 +1281,16 @@
         <v>35</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.8" customHeight="1">
@@ -1307,16 +1307,16 @@
         <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1333,24 +1333,24 @@
         <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.8" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>30</v>
+      <c r="B13" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>43</v>
@@ -1359,16 +1359,16 @@
         <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28.8" customHeight="1">
@@ -1411,24 +1411,24 @@
         <v>50</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="5" customFormat="1" ht="28.8" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
+      <c r="B16" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>52</v>
@@ -1437,24 +1437,24 @@
         <v>53</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>30</v>
+      <c r="B17" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>55</v>
@@ -1463,16 +1463,16 @@
         <v>56</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1489,16 +1489,16 @@
         <v>59</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8" customHeight="1">
@@ -1515,16 +1515,16 @@
         <v>62</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1541,16 +1541,16 @@
         <v>65</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="28.8" customHeight="1">
@@ -1567,16 +1567,16 @@
         <v>68</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1593,16 +1593,16 @@
         <v>71</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.8" customHeight="1">
@@ -1619,16 +1619,16 @@
         <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1645,16 +1645,16 @@
         <v>77</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8" customHeight="1">
@@ -1671,16 +1671,16 @@
         <v>80</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1697,16 +1697,16 @@
         <v>83</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="28.8" customHeight="1">
@@ -1723,16 +1723,16 @@
         <v>86</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1749,16 +1749,16 @@
         <v>89</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8" customHeight="1">
@@ -1775,16 +1775,16 @@
         <v>92</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1801,16 +1801,16 @@
         <v>95</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="28.8" customHeight="1">
@@ -1827,16 +1827,16 @@
         <v>98</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1853,16 +1853,16 @@
         <v>101</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="28.8" customHeight="1">
@@ -1879,16 +1879,16 @@
         <v>104</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1905,16 +1905,16 @@
         <v>107</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="28.8" customHeight="1">
@@ -1931,16 +1931,16 @@
         <v>110</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -1957,16 +1957,16 @@
         <v>113</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8" customHeight="1">
@@ -1983,16 +1983,16 @@
         <v>116</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -2009,24 +2009,24 @@
         <v>119</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>30</v>
+      <c r="B39" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>121</v>
@@ -2035,24 +2035,24 @@
         <v>122</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>30</v>
+      <c r="B40" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>124</v>
@@ -2061,24 +2061,24 @@
         <v>125</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>30</v>
+      <c r="B41" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>127</v>
@@ -2087,24 +2087,24 @@
         <v>128</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>30</v>
+      <c r="B42" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>130</v>
@@ -2113,24 +2113,24 @@
         <v>131</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>30</v>
+      <c r="B43" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>133</v>
@@ -2139,24 +2139,24 @@
         <v>134</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>30</v>
+      <c r="B44" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>136</v>
@@ -2165,16 +2165,16 @@
         <v>137</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8" customHeight="1">
@@ -2191,16 +2191,16 @@
         <v>140</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -2217,16 +2217,16 @@
         <v>143</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8" customHeight="1">
@@ -2243,16 +2243,16 @@
         <v>146</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
@@ -2269,16 +2269,16 @@
         <v>149</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8" customHeight="1">
@@ -2295,68 +2295,68 @@
         <v>152</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="5" customFormat="1" ht="28.8" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="D50" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>156</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="28.8" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/IT23650220_Assignment 1 - Test cases.xlsx
+++ b/IT23650220_Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wikum Surindu\Videos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wikum Surindu\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98FE8C57-4485-4A9E-B0A9-4D8EC4068956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A84D5700-9118-4957-AFA8-FD2C5D26AD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="237">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -745,6 +745,7 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -2051,8 +2052,8 @@
       <c r="A40" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>7</v>
+      <c r="B40" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>124</v>
@@ -2077,8 +2078,8 @@
       <c r="A41" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>7</v>
+      <c r="B41" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>127</v>
@@ -2129,8 +2130,8 @@
       <c r="A43" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>7</v>
+      <c r="B43" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>133</v>
